--- a/_handoff/Truman_Homes_Timesheet_TEMPLATE.xlsx
+++ b/_handoff/Truman_Homes_Timesheet_TEMPLATE.xlsx
@@ -584,6 +584,8 @@
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="11.43"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="15.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="15.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="15.29"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="15.29"/>
   </cols>
   <sheetData>
